--- a/research/traditional_assets/database/data/brazil/brazil_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/brazil/brazil_bank_money_center.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ4"/>
+  <dimension ref="A1:AQ5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,13 +588,13 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.23285</v>
+        <v>0.08210000000000001</v>
       </c>
       <c r="E2">
-        <v>-0.02850000000000001</v>
+        <v>0.17715</v>
       </c>
       <c r="F2">
-        <v>0.192</v>
+        <v>0.179</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -603,34 +603,34 @@
         <v>0</v>
       </c>
       <c r="I2">
-        <v>-5.703122291715823e-05</v>
+        <v>-4.83185277207264e-05</v>
       </c>
       <c r="J2">
-        <v>-5.271098892307122e-05</v>
+        <v>-4.470165499065256e-05</v>
       </c>
       <c r="K2">
-        <v>3241.33</v>
+        <v>5131.940000000001</v>
       </c>
       <c r="L2">
-        <v>0.2416431552654543</v>
+        <v>0.3203718154407037</v>
       </c>
       <c r="M2">
-        <v>725.35</v>
+        <v>1072.43</v>
       </c>
       <c r="N2">
-        <v>0.04883229320245862</v>
+        <v>0.05369855742991193</v>
       </c>
       <c r="O2">
-        <v>0.2237815958264046</v>
+        <v>0.2089716559429767</v>
       </c>
       <c r="P2">
-        <v>725.35</v>
+        <v>1072.43</v>
       </c>
       <c r="Q2">
-        <v>0.04883229320245862</v>
+        <v>0.05369855742991193</v>
       </c>
       <c r="R2">
-        <v>0.2237815958264046</v>
+        <v>0.2089716559429767</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -639,64 +639,64 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>9257.684000000001</v>
+        <v>8677.078000000001</v>
       </c>
       <c r="V2">
-        <v>0.623249382317102</v>
+        <v>0.4344773750331727</v>
       </c>
       <c r="W2">
-        <v>0.08528296273470098</v>
+        <v>0.06044815007816571</v>
       </c>
       <c r="X2">
-        <v>0.2141553176678599</v>
+        <v>0.1795809286970425</v>
       </c>
       <c r="Y2">
-        <v>-0.1288723549331589</v>
+        <v>-0.1191327786188768</v>
       </c>
       <c r="Z2">
-        <v>0.08372591355538118</v>
+        <v>0.08397075911365309</v>
       </c>
       <c r="AA2">
-        <v>-0.002046351876223798</v>
+        <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.06375916648955489</v>
+        <v>0.09362073747289357</v>
       </c>
       <c r="AC2">
-        <v>-0.06580551836577869</v>
+        <v>-0.09362073747289357</v>
       </c>
       <c r="AD2">
-        <v>171384.4</v>
+        <v>180459.8</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>171384.4</v>
+        <v>180459.8</v>
       </c>
       <c r="AG2">
-        <v>162126.716</v>
+        <v>171782.722</v>
       </c>
       <c r="AH2">
-        <v>0.9202425065091338</v>
+        <v>0.900358277732348</v>
       </c>
       <c r="AI2">
-        <v>0.8621834746540765</v>
+        <v>0.8546545715971724</v>
       </c>
       <c r="AJ2">
-        <v>0.9160704695479194</v>
+        <v>0.8958493814539129</v>
       </c>
       <c r="AK2">
-        <v>0.8554514695025928</v>
+        <v>0.8484257023535295</v>
       </c>
       <c r="AL2">
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>-0.033</v>
+        <v>-1.22</v>
       </c>
       <c r="AQ2">
-        <v>23.18181818181818</v>
+        <v>0.6344262295081967</v>
       </c>
     </row>
     <row r="3">
@@ -715,47 +715,29 @@
           <t>Bank (Money Center)</t>
         </is>
       </c>
-      <c r="D3">
-        <v>-0.503</v>
-      </c>
       <c r="E3">
-        <v>-0.186</v>
-      </c>
-      <c r="G3">
-        <v>0</v>
-      </c>
-      <c r="H3">
-        <v>0</v>
-      </c>
-      <c r="I3">
-        <v>-153</v>
-      </c>
-      <c r="J3">
-        <v>-153</v>
+        <v>0.0983</v>
       </c>
       <c r="K3">
-        <v>3.53</v>
-      </c>
-      <c r="L3">
-        <v>706</v>
+        <v>11.6</v>
       </c>
       <c r="M3">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="N3">
-        <v>0.01436170212765958</v>
+        <v>0.01187446988973706</v>
       </c>
       <c r="O3">
-        <v>0.3824362606232295</v>
+        <v>0.1206896551724138</v>
       </c>
       <c r="P3">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="Q3">
-        <v>0.01436170212765958</v>
+        <v>0.01187446988973706</v>
       </c>
       <c r="R3">
-        <v>0.3824362606232295</v>
+        <v>0.1206896551724138</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -764,31 +746,31 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0.08400000000000001</v>
+        <v>0.078</v>
       </c>
       <c r="V3">
-        <v>0.0008936170212765958</v>
+        <v>0.0006615776081424936</v>
       </c>
       <c r="W3">
-        <v>0.01887700534759358</v>
+        <v>0.06044815007816571</v>
       </c>
       <c r="X3">
-        <v>0.05629700492313286</v>
+        <v>0.08803779117573551</v>
       </c>
       <c r="Y3">
-        <v>-0.03741999957553928</v>
+        <v>-0.0275896410975698</v>
       </c>
       <c r="Z3">
-        <v>2.674969772841567e-05</v>
+        <v>0</v>
       </c>
       <c r="AA3">
-        <v>-0.004092703752447597</v>
+        <v>-0.003988268594974138</v>
       </c>
       <c r="AB3">
-        <v>0.05629700492313286</v>
+        <v>0.08803779117573551</v>
       </c>
       <c r="AC3">
-        <v>-0.06038970867558045</v>
+        <v>-0.09202605977070966</v>
       </c>
       <c r="AD3">
         <v>0</v>
@@ -800,7 +782,7 @@
         <v>0</v>
       </c>
       <c r="AG3">
-        <v>-0.08400000000000001</v>
+        <v>-0.078</v>
       </c>
       <c r="AH3">
         <v>0</v>
@@ -809,19 +791,19 @@
         <v>0</v>
       </c>
       <c r="AJ3">
-        <v>-0.000894416286894672</v>
+        <v>-0.0006620155828283343</v>
       </c>
       <c r="AK3">
-        <v>-0.0004379196730199775</v>
+        <v>-0.0003938956277585319</v>
       </c>
       <c r="AL3">
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>-0.033</v>
+        <v>-1.22</v>
       </c>
       <c r="AQ3">
-        <v>23.18181818181818</v>
+        <v>0.6344262295081967</v>
       </c>
     </row>
     <row r="4">
@@ -832,120 +814,236 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>Inter &amp; Co, Inc. (NasdaqGS:INTR)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4">
+        <v>-4.26</v>
+      </c>
+      <c r="L4">
+        <v>-0.008738461538461539</v>
+      </c>
+      <c r="M4">
+        <v>4.03</v>
+      </c>
+      <c r="N4">
+        <v>0.004238981802882087</v>
+      </c>
+      <c r="O4">
+        <v>-0.9460093896713616</v>
+      </c>
+      <c r="P4">
+        <v>4.03</v>
+      </c>
+      <c r="Q4">
+        <v>0.004238981802882087</v>
+      </c>
+      <c r="R4">
+        <v>-0.9460093896713616</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>101.8</v>
+      </c>
+      <c r="V4">
+        <v>0.1070789944251604</v>
+      </c>
+      <c r="W4">
+        <v>-0.008606060606060605</v>
+      </c>
+      <c r="X4">
+        <v>0.1795809286970425</v>
+      </c>
+      <c r="Y4">
+        <v>-0.1881869893031031</v>
+      </c>
+      <c r="Z4">
+        <v>0.2725138353177931</v>
+      </c>
+      <c r="AA4">
+        <v>0</v>
+      </c>
+      <c r="AB4">
+        <v>0.09362073747289357</v>
+      </c>
+      <c r="AC4">
+        <v>-0.09362073747289357</v>
+      </c>
+      <c r="AD4">
+        <v>2678.1</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <v>2678.1</v>
+      </c>
+      <c r="AG4">
+        <v>2576.3</v>
+      </c>
+      <c r="AH4">
+        <v>0.7380125661375661</v>
+      </c>
+      <c r="AI4">
+        <v>0.6699604743083004</v>
+      </c>
+      <c r="AJ4">
+        <v>0.7304508080521689</v>
+      </c>
+      <c r="AK4">
+        <v>0.6613358661053497</v>
+      </c>
+      <c r="AL4">
+        <v>0</v>
+      </c>
+      <c r="AM4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
           <t>Banco do Brasil S.A. (BOVESPA:BBAS3)</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>Bank (Money Center)</t>
         </is>
       </c>
-      <c r="D4">
-        <v>0.0373</v>
-      </c>
-      <c r="E4">
-        <v>0.129</v>
-      </c>
-      <c r="F4">
-        <v>0.192</v>
-      </c>
-      <c r="G4">
-        <v>0</v>
-      </c>
-      <c r="H4">
-        <v>0</v>
-      </c>
-      <c r="I4">
-        <v>0</v>
-      </c>
-      <c r="J4">
-        <v>0</v>
-      </c>
-      <c r="K4">
-        <v>3237.8</v>
-      </c>
-      <c r="L4">
-        <v>0.2413800815584067</v>
-      </c>
-      <c r="M4">
-        <v>724</v>
-      </c>
-      <c r="N4">
-        <v>0.04905182284432821</v>
-      </c>
-      <c r="O4">
-        <v>0.2236086231391686</v>
-      </c>
-      <c r="P4">
-        <v>724</v>
-      </c>
-      <c r="Q4">
-        <v>0.04905182284432821</v>
-      </c>
-      <c r="R4">
-        <v>0.2236086231391686</v>
-      </c>
-      <c r="S4">
-        <v>0</v>
-      </c>
-      <c r="T4">
-        <v>0</v>
-      </c>
-      <c r="U4">
-        <v>9257.6</v>
-      </c>
-      <c r="V4">
-        <v>0.6272129214967581</v>
-      </c>
-      <c r="W4">
-        <v>0.1516889201218084</v>
-      </c>
-      <c r="X4">
-        <v>0.3720136304125869</v>
-      </c>
-      <c r="Y4">
-        <v>-0.2203247102907785</v>
-      </c>
-      <c r="Z4">
-        <v>0.0838236801255821</v>
-      </c>
-      <c r="AA4">
-        <v>0</v>
-      </c>
-      <c r="AB4">
-        <v>0.07122132805597692</v>
-      </c>
-      <c r="AC4">
-        <v>-0.07122132805597692</v>
-      </c>
-      <c r="AD4">
-        <v>171384.4</v>
-      </c>
-      <c r="AE4">
-        <v>0</v>
-      </c>
-      <c r="AF4">
-        <v>171384.4</v>
-      </c>
-      <c r="AG4">
-        <v>162126.8</v>
-      </c>
-      <c r="AH4">
-        <v>0.9207072147790719</v>
-      </c>
-      <c r="AI4">
-        <v>0.8630166233944113</v>
-      </c>
-      <c r="AJ4">
-        <v>0.9165573217206269</v>
-      </c>
-      <c r="AK4">
-        <v>0.8563185971584006</v>
-      </c>
-      <c r="AL4">
-        <v>0</v>
-      </c>
-      <c r="AM4">
+      <c r="D5">
+        <v>0.08210000000000001</v>
+      </c>
+      <c r="E5">
+        <v>0.256</v>
+      </c>
+      <c r="F5">
+        <v>0.179</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <v>5124.6</v>
+      </c>
+      <c r="L5">
+        <v>0.3299551869784692</v>
+      </c>
+      <c r="M5">
+        <v>1067</v>
+      </c>
+      <c r="N5">
+        <v>0.05644696260322599</v>
+      </c>
+      <c r="O5">
+        <v>0.2082113725949342</v>
+      </c>
+      <c r="P5">
+        <v>1067</v>
+      </c>
+      <c r="Q5">
+        <v>0.05644696260322599</v>
+      </c>
+      <c r="R5">
+        <v>0.2082113725949342</v>
+      </c>
+      <c r="S5">
+        <v>0</v>
+      </c>
+      <c r="T5">
+        <v>0</v>
+      </c>
+      <c r="U5">
+        <v>8575.200000000001</v>
+      </c>
+      <c r="V5">
+        <v>0.4536494786459078</v>
+      </c>
+      <c r="W5">
+        <v>0.192237139738237</v>
+      </c>
+      <c r="X5">
+        <v>0.3936746380202809</v>
+      </c>
+      <c r="Y5">
+        <v>-0.2014374982820439</v>
+      </c>
+      <c r="Z5">
+        <v>0.08226946597840396</v>
+      </c>
+      <c r="AA5">
+        <v>0</v>
+      </c>
+      <c r="AB5">
+        <v>0.1058524776253926</v>
+      </c>
+      <c r="AC5">
+        <v>-0.1058524776253926</v>
+      </c>
+      <c r="AD5">
+        <v>177781.7</v>
+      </c>
+      <c r="AE5">
+        <v>0</v>
+      </c>
+      <c r="AF5">
+        <v>177781.7</v>
+      </c>
+      <c r="AG5">
+        <v>169206.5</v>
+      </c>
+      <c r="AH5">
+        <v>0.9038932421686722</v>
+      </c>
+      <c r="AI5">
+        <v>0.8590401050668772</v>
+      </c>
+      <c r="AJ5">
+        <v>0.8995120919125699</v>
+      </c>
+      <c r="AK5">
+        <v>0.8529469141596351</v>
+      </c>
+      <c r="AL5">
+        <v>0</v>
+      </c>
+      <c r="AM5">
         <v>0</v>
       </c>
     </row>

--- a/research/traditional_assets/database/data/brazil/brazil_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/brazil/brazil_bank_money_center.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ5"/>
+  <dimension ref="A1:AQ6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,13 +588,13 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.08210000000000001</v>
+        <v>0.519</v>
       </c>
       <c r="E2">
-        <v>0.17715</v>
+        <v>0.226</v>
       </c>
       <c r="F2">
-        <v>0.179</v>
+        <v>0.13</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -603,100 +603,100 @@
         <v>0</v>
       </c>
       <c r="I2">
-        <v>-4.83185277207264e-05</v>
+        <v>6.270931351945005e-06</v>
       </c>
       <c r="J2">
-        <v>-4.470165499065256e-05</v>
+        <v>5.089560577879213e-06</v>
       </c>
       <c r="K2">
-        <v>5131.940000000001</v>
+        <v>7162.29</v>
       </c>
       <c r="L2">
-        <v>0.3203718154407037</v>
+        <v>0.3034745196805554</v>
       </c>
       <c r="M2">
-        <v>1072.43</v>
+        <v>1325.96</v>
       </c>
       <c r="N2">
-        <v>0.05369855742991193</v>
+        <v>0.01776614175021873</v>
       </c>
       <c r="O2">
-        <v>0.2089716559429767</v>
+        <v>0.1851307333269108</v>
       </c>
       <c r="P2">
-        <v>1072.43</v>
+        <v>1322.67</v>
       </c>
       <c r="Q2">
-        <v>0.05369855742991193</v>
+        <v>0.01772206002350132</v>
       </c>
       <c r="R2">
-        <v>0.2089716559429767</v>
+        <v>0.1846713830353141</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>3.289999999999999</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>0.002481221152975956</v>
       </c>
       <c r="U2">
-        <v>8677.078000000001</v>
+        <v>17854.961</v>
       </c>
       <c r="V2">
-        <v>0.4344773750331727</v>
+        <v>0.239233286125243</v>
       </c>
       <c r="W2">
-        <v>0.06044815007816571</v>
+        <v>0.05602106061830239</v>
       </c>
       <c r="X2">
-        <v>0.1795809286970425</v>
+        <v>0.09256041726636259</v>
       </c>
       <c r="Y2">
-        <v>-0.1191327786188768</v>
+        <v>-0.0365393566480602</v>
       </c>
       <c r="Z2">
-        <v>0.08397075911365309</v>
+        <v>0.116388442699285</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.09362073747289357</v>
+        <v>0.07630860436251974</v>
       </c>
       <c r="AC2">
-        <v>-0.09362073747289357</v>
+        <v>-0.07630860436251974</v>
       </c>
       <c r="AD2">
-        <v>180459.8</v>
+        <v>213968.7</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>180459.8</v>
+        <v>213968.7</v>
       </c>
       <c r="AG2">
-        <v>171782.722</v>
+        <v>196113.739</v>
       </c>
       <c r="AH2">
-        <v>0.900358277732348</v>
+        <v>0.741395093879893</v>
       </c>
       <c r="AI2">
-        <v>0.8546545715971724</v>
+        <v>0.8366865649930748</v>
       </c>
       <c r="AJ2">
-        <v>0.8958493814539129</v>
+        <v>0.7243409207783187</v>
       </c>
       <c r="AK2">
-        <v>0.8484257023535295</v>
+        <v>0.8244283921839591</v>
       </c>
       <c r="AL2">
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>-1.22</v>
+        <v>-0.134</v>
       </c>
       <c r="AQ2">
-        <v>0.6344262295081967</v>
+        <v>-1.104477611940298</v>
       </c>
     </row>
     <row r="3">
@@ -715,29 +715,47 @@
           <t>Bank (Money Center)</t>
         </is>
       </c>
+      <c r="D3">
+        <v>0.755</v>
+      </c>
       <c r="E3">
-        <v>0.0983</v>
+        <v>-0.07780000000000001</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3">
+        <v>0.09487179487179487</v>
+      </c>
+      <c r="J3">
+        <v>0.09177338076182007</v>
       </c>
       <c r="K3">
-        <v>11.6</v>
+        <v>6.69</v>
+      </c>
+      <c r="L3">
+        <v>4.288461538461538</v>
       </c>
       <c r="M3">
-        <v>1.4</v>
+        <v>1.57</v>
       </c>
       <c r="N3">
-        <v>0.01187446988973706</v>
+        <v>0.01263073209975865</v>
       </c>
       <c r="O3">
-        <v>0.1206896551724138</v>
+        <v>0.234678624813154</v>
       </c>
       <c r="P3">
-        <v>1.4</v>
+        <v>1.57</v>
       </c>
       <c r="Q3">
-        <v>0.01187446988973706</v>
+        <v>0.01263073209975865</v>
       </c>
       <c r="R3">
-        <v>0.1206896551724138</v>
+        <v>0.234678624813154</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -746,31 +764,31 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0.078</v>
+        <v>0.061</v>
       </c>
       <c r="V3">
-        <v>0.0006615776081424936</v>
+        <v>0.0004907481898632341</v>
       </c>
       <c r="W3">
-        <v>0.06044815007816571</v>
+        <v>0.03377082281675921</v>
       </c>
       <c r="X3">
-        <v>0.08803779117573551</v>
+        <v>0.07422920874820521</v>
       </c>
       <c r="Y3">
-        <v>-0.0275896410975698</v>
+        <v>-0.040458385931446</v>
       </c>
       <c r="Z3">
-        <v>0</v>
+        <v>0.007877912555170638</v>
       </c>
       <c r="AA3">
-        <v>-0.003988268594974138</v>
+        <v>0.0007229826685339977</v>
       </c>
       <c r="AB3">
-        <v>0.08803779117573551</v>
+        <v>0.07422920874820521</v>
       </c>
       <c r="AC3">
-        <v>-0.09202605977070966</v>
+        <v>-0.07350622607967121</v>
       </c>
       <c r="AD3">
         <v>0</v>
@@ -782,7 +800,7 @@
         <v>0</v>
       </c>
       <c r="AG3">
-        <v>-0.078</v>
+        <v>-0.061</v>
       </c>
       <c r="AH3">
         <v>0</v>
@@ -791,19 +809,19 @@
         <v>0</v>
       </c>
       <c r="AJ3">
-        <v>-0.0006620155828283343</v>
+        <v>-0.0004909891418958621</v>
       </c>
       <c r="AK3">
-        <v>-0.0003938956277585319</v>
+        <v>-0.0002768461325502975</v>
       </c>
       <c r="AL3">
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>-1.22</v>
+        <v>-0.134</v>
       </c>
       <c r="AQ3">
-        <v>0.6344262295081967</v>
+        <v>-1.104477611940298</v>
       </c>
     </row>
     <row r="4">
@@ -814,7 +832,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Inter &amp; Co, Inc. (NasdaqGS:INTR)</t>
+          <t>Nu Holdings Ltd. (NYSE:NU)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -835,85 +853,82 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>-4.26</v>
+        <v>372</v>
       </c>
       <c r="L4">
-        <v>-0.008738461538461539</v>
+        <v>0.1189334356416651</v>
       </c>
       <c r="M4">
-        <v>4.03</v>
+        <v>-0</v>
       </c>
       <c r="N4">
-        <v>0.004238981802882087</v>
+        <v>-0</v>
       </c>
       <c r="O4">
-        <v>-0.9460093896713616</v>
+        <v>-0</v>
       </c>
       <c r="P4">
-        <v>4.03</v>
+        <v>-0</v>
       </c>
       <c r="Q4">
-        <v>0.004238981802882087</v>
+        <v>-0</v>
       </c>
       <c r="R4">
-        <v>-0.9460093896713616</v>
+        <v>-0</v>
       </c>
       <c r="S4">
         <v>0</v>
       </c>
-      <c r="T4">
-        <v>0</v>
-      </c>
       <c r="U4">
-        <v>101.8</v>
+        <v>3213.6</v>
       </c>
       <c r="V4">
-        <v>0.1070789944251604</v>
+        <v>0.08113430484442694</v>
       </c>
       <c r="W4">
-        <v>-0.008606060606060605</v>
+        <v>0.07827129841984556</v>
       </c>
       <c r="X4">
-        <v>0.1795809286970425</v>
+        <v>0.07501598363154217</v>
       </c>
       <c r="Y4">
-        <v>-0.1881869893031031</v>
+        <v>0.00325531478830339</v>
       </c>
       <c r="Z4">
-        <v>0.2725138353177931</v>
+        <v>2.566715903495816</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.09362073747289357</v>
+        <v>0.07468635022855272</v>
       </c>
       <c r="AC4">
-        <v>-0.09362073747289357</v>
+        <v>-0.07468635022855272</v>
       </c>
       <c r="AD4">
-        <v>2678.1</v>
+        <v>1332.7</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>2678.1</v>
+        <v>1332.7</v>
       </c>
       <c r="AG4">
-        <v>2576.3</v>
+        <v>-1880.9</v>
       </c>
       <c r="AH4">
-        <v>0.7380125661375661</v>
+        <v>0.03255164126024948</v>
       </c>
       <c r="AI4">
-        <v>0.6699604743083004</v>
+        <v>0.1845333702575464</v>
       </c>
       <c r="AJ4">
-        <v>0.7304508080521689</v>
+        <v>-0.04985488039228679</v>
       </c>
       <c r="AK4">
-        <v>0.6613358661053497</v>
+        <v>-0.469239596846622</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -930,120 +945,242 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
+          <t>Inter &amp; Co, Inc. (NasdaqGS:INTR)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D5">
+        <v>0.519</v>
+      </c>
+      <c r="E5">
+        <v>0.622</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <v>36.8</v>
+      </c>
+      <c r="L5">
+        <v>0.06086668871981474</v>
+      </c>
+      <c r="M5">
+        <v>22.39</v>
+      </c>
+      <c r="N5">
+        <v>0.01002238137869293</v>
+      </c>
+      <c r="O5">
+        <v>0.6084239130434783</v>
+      </c>
+      <c r="P5">
+        <v>19.1</v>
+      </c>
+      <c r="Q5">
+        <v>0.008549686660698299</v>
+      </c>
+      <c r="R5">
+        <v>0.5190217391304348</v>
+      </c>
+      <c r="S5">
+        <v>3.289999999999999</v>
+      </c>
+      <c r="T5">
+        <v>0.1469405984814649</v>
+      </c>
+      <c r="U5">
+        <v>860.4</v>
+      </c>
+      <c r="V5">
+        <v>0.3851387645478961</v>
+      </c>
+      <c r="W5">
+        <v>0.02827506723011909</v>
+      </c>
+      <c r="X5">
+        <v>0.110104850901183</v>
+      </c>
+      <c r="Y5">
+        <v>-0.08182978367106392</v>
+      </c>
+      <c r="Z5">
+        <v>0.1617529027770346</v>
+      </c>
+      <c r="AA5">
+        <v>0</v>
+      </c>
+      <c r="AB5">
+        <v>0.07793085849648676</v>
+      </c>
+      <c r="AC5">
+        <v>-0.07793085849648676</v>
+      </c>
+      <c r="AD5">
+        <v>3427.5</v>
+      </c>
+      <c r="AE5">
+        <v>0</v>
+      </c>
+      <c r="AF5">
+        <v>3427.5</v>
+      </c>
+      <c r="AG5">
+        <v>2567.1</v>
+      </c>
+      <c r="AH5">
+        <v>0.6054049280226088</v>
+      </c>
+      <c r="AI5">
+        <v>0.6990760570274736</v>
+      </c>
+      <c r="AJ5">
+        <v>0.5346899668825893</v>
+      </c>
+      <c r="AK5">
+        <v>0.6350278293135436</v>
+      </c>
+      <c r="AL5">
+        <v>0</v>
+      </c>
+      <c r="AM5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
           <t>Banco do Brasil S.A. (BOVESPA:BBAS3)</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>Bank (Money Center)</t>
         </is>
       </c>
-      <c r="D5">
-        <v>0.08210000000000001</v>
-      </c>
-      <c r="E5">
-        <v>0.256</v>
-      </c>
-      <c r="F5">
-        <v>0.179</v>
-      </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
-      <c r="H5">
-        <v>0</v>
-      </c>
-      <c r="I5">
-        <v>0</v>
-      </c>
-      <c r="J5">
-        <v>0</v>
-      </c>
-      <c r="K5">
-        <v>5124.6</v>
-      </c>
-      <c r="L5">
-        <v>0.3299551869784692</v>
-      </c>
-      <c r="M5">
-        <v>1067</v>
-      </c>
-      <c r="N5">
-        <v>0.05644696260322599</v>
-      </c>
-      <c r="O5">
-        <v>0.2082113725949342</v>
-      </c>
-      <c r="P5">
-        <v>1067</v>
-      </c>
-      <c r="Q5">
-        <v>0.05644696260322599</v>
-      </c>
-      <c r="R5">
-        <v>0.2082113725949342</v>
-      </c>
-      <c r="S5">
-        <v>0</v>
-      </c>
-      <c r="T5">
-        <v>0</v>
-      </c>
-      <c r="U5">
-        <v>8575.200000000001</v>
-      </c>
-      <c r="V5">
-        <v>0.4536494786459078</v>
-      </c>
-      <c r="W5">
-        <v>0.192237139738237</v>
-      </c>
-      <c r="X5">
-        <v>0.3936746380202809</v>
-      </c>
-      <c r="Y5">
-        <v>-0.2014374982820439</v>
-      </c>
-      <c r="Z5">
-        <v>0.08226946597840396</v>
-      </c>
-      <c r="AA5">
-        <v>0</v>
-      </c>
-      <c r="AB5">
-        <v>0.1058524776253926</v>
-      </c>
-      <c r="AC5">
-        <v>-0.1058524776253926</v>
-      </c>
-      <c r="AD5">
-        <v>177781.7</v>
-      </c>
-      <c r="AE5">
-        <v>0</v>
-      </c>
-      <c r="AF5">
-        <v>177781.7</v>
-      </c>
-      <c r="AG5">
-        <v>169206.5</v>
-      </c>
-      <c r="AH5">
-        <v>0.9038932421686722</v>
-      </c>
-      <c r="AI5">
-        <v>0.8590401050668772</v>
-      </c>
-      <c r="AJ5">
-        <v>0.8995120919125699</v>
-      </c>
-      <c r="AK5">
-        <v>0.8529469141596351</v>
-      </c>
-      <c r="AL5">
-        <v>0</v>
-      </c>
-      <c r="AM5">
+      <c r="D6">
+        <v>0.11</v>
+      </c>
+      <c r="E6">
+        <v>0.226</v>
+      </c>
+      <c r="F6">
+        <v>0.13</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6">
+        <v>6746.8</v>
+      </c>
+      <c r="L6">
+        <v>0.3395983288870992</v>
+      </c>
+      <c r="M6">
+        <v>1302</v>
+      </c>
+      <c r="N6">
+        <v>0.03985624812504209</v>
+      </c>
+      <c r="O6">
+        <v>0.1929803758818996</v>
+      </c>
+      <c r="P6">
+        <v>1302</v>
+      </c>
+      <c r="Q6">
+        <v>0.03985624812504209</v>
+      </c>
+      <c r="R6">
+        <v>0.1929803758818996</v>
+      </c>
+      <c r="S6">
+        <v>0</v>
+      </c>
+      <c r="T6">
+        <v>0</v>
+      </c>
+      <c r="U6">
+        <v>13780.9</v>
+      </c>
+      <c r="V6">
+        <v>0.4218548155041417</v>
+      </c>
+      <c r="W6">
+        <v>0.2372734722012189</v>
+      </c>
+      <c r="X6">
+        <v>0.223980351114701</v>
+      </c>
+      <c r="Y6">
+        <v>0.01329312108651792</v>
+      </c>
+      <c r="Z6">
+        <v>0.1005297457635266</v>
+      </c>
+      <c r="AA6">
+        <v>0</v>
+      </c>
+      <c r="AB6">
+        <v>0.08371643791299582</v>
+      </c>
+      <c r="AC6">
+        <v>-0.08371643791299582</v>
+      </c>
+      <c r="AD6">
+        <v>209208.5</v>
+      </c>
+      <c r="AE6">
+        <v>0</v>
+      </c>
+      <c r="AF6">
+        <v>209208.5</v>
+      </c>
+      <c r="AG6">
+        <v>195427.6</v>
+      </c>
+      <c r="AH6">
+        <v>0.8649414844554584</v>
+      </c>
+      <c r="AI6">
+        <v>0.8595674973427213</v>
+      </c>
+      <c r="AJ6">
+        <v>0.856781604156163</v>
+      </c>
+      <c r="AK6">
+        <v>0.8511388144622642</v>
+      </c>
+      <c r="AL6">
+        <v>0</v>
+      </c>
+      <c r="AM6">
         <v>0</v>
       </c>
     </row>

--- a/research/traditional_assets/database/data/brazil/brazil_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/brazil/brazil_bank_money_center.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ6"/>
+  <dimension ref="A1:AQ4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,13 +588,13 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.519</v>
+        <v>0.118</v>
       </c>
       <c r="E2">
-        <v>0.226</v>
+        <v>0.142</v>
       </c>
       <c r="F2">
-        <v>0.13</v>
+        <v>0.0281</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -603,100 +603,97 @@
         <v>0</v>
       </c>
       <c r="I2">
-        <v>6.270931351945005e-06</v>
+        <v>0</v>
       </c>
       <c r="J2">
-        <v>5.089560577879213e-06</v>
+        <v>0</v>
       </c>
       <c r="K2">
-        <v>7162.29</v>
+        <v>7578.2</v>
       </c>
       <c r="L2">
-        <v>0.3034745196805554</v>
+        <v>0.2934568364964238</v>
       </c>
       <c r="M2">
-        <v>1325.96</v>
+        <v>1303.4</v>
       </c>
       <c r="N2">
-        <v>0.01776614175021873</v>
+        <v>0.01807696788474234</v>
       </c>
       <c r="O2">
-        <v>0.1851307333269108</v>
+        <v>0.1719933493441715</v>
       </c>
       <c r="P2">
-        <v>1322.67</v>
+        <v>1303.4</v>
       </c>
       <c r="Q2">
-        <v>0.01772206002350132</v>
+        <v>0.01807696788474234</v>
       </c>
       <c r="R2">
-        <v>0.1846713830353141</v>
+        <v>0.1719933493441715</v>
       </c>
       <c r="S2">
-        <v>3.289999999999999</v>
+        <v>0</v>
       </c>
       <c r="T2">
-        <v>0.002481221152975956</v>
+        <v>0</v>
       </c>
       <c r="U2">
-        <v>17854.961</v>
+        <v>21645.6</v>
       </c>
       <c r="V2">
-        <v>0.239233286125243</v>
+        <v>0.3002047077228623</v>
       </c>
       <c r="W2">
-        <v>0.05602106061830239</v>
+        <v>0.2385263531385284</v>
       </c>
       <c r="X2">
-        <v>0.09256041726636259</v>
+        <v>0.1671691040233007</v>
       </c>
       <c r="Y2">
-        <v>-0.0365393566480602</v>
+        <v>0.07135724911522762</v>
       </c>
       <c r="Z2">
-        <v>0.116388442699285</v>
+        <v>0.1112068078260199</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.07630860436251974</v>
+        <v>0.07728539947914062</v>
       </c>
       <c r="AC2">
-        <v>-0.07630860436251974</v>
+        <v>-0.07728539947914062</v>
       </c>
       <c r="AD2">
-        <v>213968.7</v>
+        <v>205186.1</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>213968.7</v>
+        <v>205186.1</v>
       </c>
       <c r="AG2">
-        <v>196113.739</v>
+        <v>183540.5</v>
       </c>
       <c r="AH2">
-        <v>0.741395093879893</v>
+        <v>0.7399722816167542</v>
       </c>
       <c r="AI2">
-        <v>0.8366865649930748</v>
+        <v>0.8298746812430359</v>
       </c>
       <c r="AJ2">
-        <v>0.7243409207783187</v>
+        <v>0.7179554480794137</v>
       </c>
       <c r="AK2">
-        <v>0.8244283921839591</v>
+        <v>0.8135519820357715</v>
       </c>
       <c r="AL2">
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>-0.134</v>
-      </c>
-      <c r="AQ2">
-        <v>-1.104477611940298</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -707,7 +704,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Alfa Holdings S.A. (BOVESPA:RPAD3)</t>
+          <t>Nu Holdings Ltd. (NYSE:NU)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -715,12 +712,6 @@
           <t>Bank (Money Center)</t>
         </is>
       </c>
-      <c r="D3">
-        <v>0.755</v>
-      </c>
-      <c r="E3">
-        <v>-0.07780000000000001</v>
-      </c>
       <c r="G3">
         <v>0</v>
       </c>
@@ -728,100 +719,94 @@
         <v>0</v>
       </c>
       <c r="I3">
-        <v>0.09487179487179487</v>
+        <v>0</v>
       </c>
       <c r="J3">
-        <v>0.09177338076182007</v>
+        <v>0</v>
       </c>
       <c r="K3">
-        <v>6.69</v>
+        <v>1780.3</v>
       </c>
       <c r="L3">
-        <v>4.288461538461538</v>
+        <v>0.3259727181177332</v>
       </c>
       <c r="M3">
-        <v>1.57</v>
+        <v>-0</v>
       </c>
       <c r="N3">
-        <v>0.01263073209975865</v>
+        <v>-0</v>
       </c>
       <c r="O3">
-        <v>0.234678624813154</v>
+        <v>-0</v>
       </c>
       <c r="P3">
-        <v>1.57</v>
+        <v>-0</v>
       </c>
       <c r="Q3">
-        <v>0.01263073209975865</v>
+        <v>-0</v>
       </c>
       <c r="R3">
-        <v>0.234678624813154</v>
+        <v>-0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
-      <c r="T3">
-        <v>0</v>
-      </c>
       <c r="U3">
-        <v>0.061</v>
+        <v>7645.8</v>
       </c>
       <c r="V3">
-        <v>0.0004907481898632341</v>
+        <v>0.1535415281858291</v>
       </c>
       <c r="W3">
-        <v>0.03377082281675921</v>
+        <v>0.3022939907968689</v>
       </c>
       <c r="X3">
-        <v>0.07422920874820521</v>
+        <v>0.07686908358813088</v>
       </c>
       <c r="Y3">
-        <v>-0.040458385931446</v>
+        <v>0.225424907208738</v>
       </c>
       <c r="Z3">
-        <v>0.007877912555170638</v>
+        <v>1.512503807914924</v>
       </c>
       <c r="AA3">
-        <v>0.0007229826685339977</v>
+        <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.07422920874820521</v>
+        <v>0.07622143168516161</v>
       </c>
       <c r="AC3">
-        <v>-0.07350622607967121</v>
+        <v>-0.07622143168516161</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>2153.3</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0</v>
+        <v>2153.3</v>
       </c>
       <c r="AG3">
-        <v>-0.061</v>
+        <v>-5492.5</v>
       </c>
       <c r="AH3">
-        <v>0</v>
+        <v>0.04144978979626407</v>
       </c>
       <c r="AI3">
-        <v>0</v>
+        <v>0.2197783130562587</v>
       </c>
       <c r="AJ3">
-        <v>-0.0004909891418958621</v>
+        <v>-0.1239735643443677</v>
       </c>
       <c r="AK3">
-        <v>-0.0002768461325502975</v>
+        <v>-2.552514174179756</v>
       </c>
       <c r="AL3">
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>-0.134</v>
-      </c>
-      <c r="AQ3">
-        <v>-1.104477611940298</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -832,7 +817,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Nu Holdings Ltd. (NYSE:NU)</t>
+          <t>Banco do Brasil S.A. (BOVESPA:BBAS3)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -840,6 +825,15 @@
           <t>Bank (Money Center)</t>
         </is>
       </c>
+      <c r="D4">
+        <v>0.118</v>
+      </c>
+      <c r="E4">
+        <v>0.142</v>
+      </c>
+      <c r="F4">
+        <v>0.0281</v>
+      </c>
       <c r="G4">
         <v>0</v>
       </c>
@@ -853,334 +847,90 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>372</v>
+        <v>5797.9</v>
       </c>
       <c r="L4">
-        <v>0.1189334356416651</v>
+        <v>0.284735591089459</v>
       </c>
       <c r="M4">
-        <v>-0</v>
+        <v>1303.4</v>
       </c>
       <c r="N4">
-        <v>-0</v>
+        <v>0.05843139891959743</v>
       </c>
       <c r="O4">
-        <v>-0</v>
+        <v>0.2248055330378241</v>
       </c>
       <c r="P4">
-        <v>-0</v>
+        <v>1303.4</v>
       </c>
       <c r="Q4">
-        <v>-0</v>
+        <v>0.05843139891959743</v>
       </c>
       <c r="R4">
-        <v>-0</v>
+        <v>0.2248055330378241</v>
       </c>
       <c r="S4">
         <v>0</v>
       </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
       <c r="U4">
-        <v>3213.6</v>
+        <v>13999.8</v>
       </c>
       <c r="V4">
-        <v>0.08113430484442694</v>
+        <v>0.6276107860937394</v>
       </c>
       <c r="W4">
-        <v>0.07827129841984556</v>
+        <v>0.1747587154801878</v>
       </c>
       <c r="X4">
-        <v>0.07501598363154217</v>
+        <v>0.2574691244584706</v>
       </c>
       <c r="Y4">
-        <v>0.00325531478830339</v>
+        <v>-0.08271040897828275</v>
       </c>
       <c r="Z4">
-        <v>2.566715903495816</v>
+        <v>0.08907272919745132</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.07468635022855272</v>
+        <v>0.07834936727311964</v>
       </c>
       <c r="AC4">
-        <v>-0.07468635022855272</v>
+        <v>-0.07834936727311964</v>
       </c>
       <c r="AD4">
-        <v>1332.7</v>
+        <v>203032.8</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>1332.7</v>
+        <v>203032.8</v>
       </c>
       <c r="AG4">
-        <v>-1880.9</v>
+        <v>189033</v>
       </c>
       <c r="AH4">
-        <v>0.03255164126024948</v>
+        <v>0.9010092780087627</v>
       </c>
       <c r="AI4">
-        <v>0.1845333702575464</v>
+        <v>0.8550481171134028</v>
       </c>
       <c r="AJ4">
-        <v>-0.04985488039228679</v>
+        <v>0.8944518180463188</v>
       </c>
       <c r="AK4">
-        <v>-0.469239596846622</v>
+        <v>0.8459665404800403</v>
       </c>
       <c r="AL4">
         <v>0</v>
       </c>
       <c r="AM4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Brazil</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Inter &amp; Co, Inc. (NasdaqGS:INTR)</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Bank (Money Center)</t>
-        </is>
-      </c>
-      <c r="D5">
-        <v>0.519</v>
-      </c>
-      <c r="E5">
-        <v>0.622</v>
-      </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
-      <c r="H5">
-        <v>0</v>
-      </c>
-      <c r="I5">
-        <v>0</v>
-      </c>
-      <c r="J5">
-        <v>0</v>
-      </c>
-      <c r="K5">
-        <v>36.8</v>
-      </c>
-      <c r="L5">
-        <v>0.06086668871981474</v>
-      </c>
-      <c r="M5">
-        <v>22.39</v>
-      </c>
-      <c r="N5">
-        <v>0.01002238137869293</v>
-      </c>
-      <c r="O5">
-        <v>0.6084239130434783</v>
-      </c>
-      <c r="P5">
-        <v>19.1</v>
-      </c>
-      <c r="Q5">
-        <v>0.008549686660698299</v>
-      </c>
-      <c r="R5">
-        <v>0.5190217391304348</v>
-      </c>
-      <c r="S5">
-        <v>3.289999999999999</v>
-      </c>
-      <c r="T5">
-        <v>0.1469405984814649</v>
-      </c>
-      <c r="U5">
-        <v>860.4</v>
-      </c>
-      <c r="V5">
-        <v>0.3851387645478961</v>
-      </c>
-      <c r="W5">
-        <v>0.02827506723011909</v>
-      </c>
-      <c r="X5">
-        <v>0.110104850901183</v>
-      </c>
-      <c r="Y5">
-        <v>-0.08182978367106392</v>
-      </c>
-      <c r="Z5">
-        <v>0.1617529027770346</v>
-      </c>
-      <c r="AA5">
-        <v>0</v>
-      </c>
-      <c r="AB5">
-        <v>0.07793085849648676</v>
-      </c>
-      <c r="AC5">
-        <v>-0.07793085849648676</v>
-      </c>
-      <c r="AD5">
-        <v>3427.5</v>
-      </c>
-      <c r="AE5">
-        <v>0</v>
-      </c>
-      <c r="AF5">
-        <v>3427.5</v>
-      </c>
-      <c r="AG5">
-        <v>2567.1</v>
-      </c>
-      <c r="AH5">
-        <v>0.6054049280226088</v>
-      </c>
-      <c r="AI5">
-        <v>0.6990760570274736</v>
-      </c>
-      <c r="AJ5">
-        <v>0.5346899668825893</v>
-      </c>
-      <c r="AK5">
-        <v>0.6350278293135436</v>
-      </c>
-      <c r="AL5">
-        <v>0</v>
-      </c>
-      <c r="AM5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Brazil</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Banco do Brasil S.A. (BOVESPA:BBAS3)</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Bank (Money Center)</t>
-        </is>
-      </c>
-      <c r="D6">
-        <v>0.11</v>
-      </c>
-      <c r="E6">
-        <v>0.226</v>
-      </c>
-      <c r="F6">
-        <v>0.13</v>
-      </c>
-      <c r="G6">
-        <v>0</v>
-      </c>
-      <c r="H6">
-        <v>0</v>
-      </c>
-      <c r="I6">
-        <v>0</v>
-      </c>
-      <c r="J6">
-        <v>0</v>
-      </c>
-      <c r="K6">
-        <v>6746.8</v>
-      </c>
-      <c r="L6">
-        <v>0.3395983288870992</v>
-      </c>
-      <c r="M6">
-        <v>1302</v>
-      </c>
-      <c r="N6">
-        <v>0.03985624812504209</v>
-      </c>
-      <c r="O6">
-        <v>0.1929803758818996</v>
-      </c>
-      <c r="P6">
-        <v>1302</v>
-      </c>
-      <c r="Q6">
-        <v>0.03985624812504209</v>
-      </c>
-      <c r="R6">
-        <v>0.1929803758818996</v>
-      </c>
-      <c r="S6">
-        <v>0</v>
-      </c>
-      <c r="T6">
-        <v>0</v>
-      </c>
-      <c r="U6">
-        <v>13780.9</v>
-      </c>
-      <c r="V6">
-        <v>0.4218548155041417</v>
-      </c>
-      <c r="W6">
-        <v>0.2372734722012189</v>
-      </c>
-      <c r="X6">
-        <v>0.223980351114701</v>
-      </c>
-      <c r="Y6">
-        <v>0.01329312108651792</v>
-      </c>
-      <c r="Z6">
-        <v>0.1005297457635266</v>
-      </c>
-      <c r="AA6">
-        <v>0</v>
-      </c>
-      <c r="AB6">
-        <v>0.08371643791299582</v>
-      </c>
-      <c r="AC6">
-        <v>-0.08371643791299582</v>
-      </c>
-      <c r="AD6">
-        <v>209208.5</v>
-      </c>
-      <c r="AE6">
-        <v>0</v>
-      </c>
-      <c r="AF6">
-        <v>209208.5</v>
-      </c>
-      <c r="AG6">
-        <v>195427.6</v>
-      </c>
-      <c r="AH6">
-        <v>0.8649414844554584</v>
-      </c>
-      <c r="AI6">
-        <v>0.8595674973427213</v>
-      </c>
-      <c r="AJ6">
-        <v>0.856781604156163</v>
-      </c>
-      <c r="AK6">
-        <v>0.8511388144622642</v>
-      </c>
-      <c r="AL6">
-        <v>0</v>
-      </c>
-      <c r="AM6">
         <v>0</v>
       </c>
     </row>

--- a/research/traditional_assets/database/data/brazil/brazil_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/brazil/brazil_bank_money_center.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ4"/>
+  <dimension ref="A1:AQ6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,10 +588,10 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.118</v>
+        <v>0.3055</v>
       </c>
       <c r="E2">
-        <v>0.142</v>
+        <v>0.2955</v>
       </c>
       <c r="F2">
         <v>0.0281</v>
@@ -603,97 +603,100 @@
         <v>0</v>
       </c>
       <c r="I2">
-        <v>0</v>
+        <v>-6.242572842551782E-05</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>-5.252151618006735E-05</v>
       </c>
       <c r="K2">
-        <v>7578.2</v>
+        <v>7707.099999999999</v>
       </c>
       <c r="L2">
-        <v>0.2934568364964238</v>
+        <v>0.28983212743874</v>
       </c>
       <c r="M2">
-        <v>1303.4</v>
+        <v>1312.71</v>
       </c>
       <c r="N2">
-        <v>0.01807696788474234</v>
+        <v>0.01772902232486528</v>
       </c>
       <c r="O2">
-        <v>0.1719933493441715</v>
+        <v>0.1703247654759897</v>
       </c>
       <c r="P2">
-        <v>1303.4</v>
+        <v>1309.23</v>
       </c>
       <c r="Q2">
-        <v>0.01807696788474234</v>
+        <v>0.01768202260848426</v>
       </c>
       <c r="R2">
-        <v>0.1719933493441715</v>
+        <v>0.1698732337714575</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>0.002651004410722856</v>
       </c>
       <c r="U2">
-        <v>21645.6</v>
+        <v>21758.02</v>
       </c>
       <c r="V2">
-        <v>0.3002047077228623</v>
+        <v>0.2938565428197129</v>
       </c>
       <c r="W2">
-        <v>0.2385263531385284</v>
+        <v>0.1368359542458031</v>
       </c>
       <c r="X2">
-        <v>0.1671691040233007</v>
+        <v>0.09569606755434873</v>
       </c>
       <c r="Y2">
-        <v>0.07135724911522762</v>
+        <v>0.04113988669145438</v>
       </c>
       <c r="Z2">
-        <v>0.1112068078260199</v>
+        <v>0.1126488540782652</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.07728539947914062</v>
+        <v>0.07610966154081442</v>
       </c>
       <c r="AC2">
-        <v>-0.07728539947914062</v>
+        <v>-0.07728155556809174</v>
       </c>
       <c r="AD2">
-        <v>205186.1</v>
+        <v>208766.4</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>205186.1</v>
+        <v>208766.4</v>
       </c>
       <c r="AG2">
-        <v>183540.5</v>
+        <v>187008.38</v>
       </c>
       <c r="AH2">
-        <v>0.7399722816167542</v>
+        <v>0.7381876274268111</v>
       </c>
       <c r="AI2">
-        <v>0.8298746812430359</v>
+        <v>0.8263280076471391</v>
       </c>
       <c r="AJ2">
-        <v>0.7179554480794137</v>
+        <v>0.7163661804814057</v>
       </c>
       <c r="AK2">
-        <v>0.8135519820357715</v>
+        <v>0.8099616311948243</v>
       </c>
       <c r="AL2">
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>0</v>
+        <v>-1.26</v>
+      </c>
+      <c r="AQ2">
+        <v>1.317460317460317</v>
       </c>
     </row>
     <row r="3">
@@ -704,7 +707,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Nu Holdings Ltd. (NYSE:NU)</t>
+          <t>Inter &amp; Co, Inc. (NasdaqGS:INTR)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -712,6 +715,12 @@
           <t>Bank (Money Center)</t>
         </is>
       </c>
+      <c r="D3">
+        <v>0.493</v>
+      </c>
+      <c r="E3">
+        <v>0.449</v>
+      </c>
       <c r="G3">
         <v>0</v>
       </c>
@@ -725,82 +734,85 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>1780.3</v>
+        <v>143.8</v>
       </c>
       <c r="L3">
-        <v>0.3259727181177332</v>
+        <v>0.1873127523772307</v>
       </c>
       <c r="M3">
-        <v>-0</v>
+        <v>7.81</v>
       </c>
       <c r="N3">
-        <v>-0</v>
+        <v>0.004215924426450742</v>
       </c>
       <c r="O3">
-        <v>-0</v>
+        <v>0.0543115438108484</v>
       </c>
       <c r="P3">
-        <v>-0</v>
+        <v>4.33</v>
       </c>
       <c r="Q3">
-        <v>-0</v>
+        <v>0.002337381916329285</v>
       </c>
       <c r="R3">
-        <v>-0</v>
+        <v>0.03011126564673157</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>3.48</v>
+      </c>
+      <c r="T3">
+        <v>0.4455825864276569</v>
       </c>
       <c r="U3">
-        <v>7645.8</v>
+        <v>112.4</v>
       </c>
       <c r="V3">
-        <v>0.1535415281858291</v>
+        <v>0.06067476383265857</v>
       </c>
       <c r="W3">
-        <v>0.3022939907968689</v>
+        <v>0.09891319301141836</v>
       </c>
       <c r="X3">
-        <v>0.07686908358813088</v>
+        <v>0.1145277594278772</v>
       </c>
       <c r="Y3">
-        <v>0.225424907208738</v>
+        <v>-0.01561456641645888</v>
       </c>
       <c r="Z3">
-        <v>1.512503807914924</v>
+        <v>0.2119547211485368</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.07622143168516161</v>
+        <v>0.07497650916552823</v>
       </c>
       <c r="AC3">
-        <v>-0.07622143168516161</v>
+        <v>-0.07497650916552823</v>
       </c>
       <c r="AD3">
-        <v>2153.3</v>
+        <v>3580.3</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>2153.3</v>
+        <v>3580.3</v>
       </c>
       <c r="AG3">
-        <v>-5492.5</v>
+        <v>3467.9</v>
       </c>
       <c r="AH3">
-        <v>0.04144978979626407</v>
+        <v>0.6590156088941246</v>
       </c>
       <c r="AI3">
-        <v>0.2197783130562587</v>
+        <v>0.687356012901244</v>
       </c>
       <c r="AJ3">
-        <v>-0.1239735643443677</v>
+        <v>0.6518118938425683</v>
       </c>
       <c r="AK3">
-        <v>-2.552514174179756</v>
+        <v>0.6804607173691234</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -817,121 +829,338 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>Nu Holdings Ltd. (NYSE:NU)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4">
+        <v>1780.3</v>
+      </c>
+      <c r="L4">
+        <v>0.3259727181177332</v>
+      </c>
+      <c r="M4">
+        <v>-0</v>
+      </c>
+      <c r="N4">
+        <v>-0</v>
+      </c>
+      <c r="O4">
+        <v>-0</v>
+      </c>
+      <c r="P4">
+        <v>-0</v>
+      </c>
+      <c r="Q4">
+        <v>-0</v>
+      </c>
+      <c r="R4">
+        <v>-0</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>7645.8</v>
+      </c>
+      <c r="V4">
+        <v>0.1535415281858291</v>
+      </c>
+      <c r="W4">
+        <v>0.3022939907968689</v>
+      </c>
+      <c r="X4">
+        <v>0.07686437568082023</v>
+      </c>
+      <c r="Y4">
+        <v>0.2254296151160486</v>
+      </c>
+      <c r="Z4">
+        <v>1.512503807914924</v>
+      </c>
+      <c r="AA4">
+        <v>0</v>
+      </c>
+      <c r="AB4">
+        <v>0.07621691891961938</v>
+      </c>
+      <c r="AC4">
+        <v>-0.07621691891961938</v>
+      </c>
+      <c r="AD4">
+        <v>2153.3</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <v>2153.3</v>
+      </c>
+      <c r="AG4">
+        <v>-5492.5</v>
+      </c>
+      <c r="AH4">
+        <v>0.04144978979626407</v>
+      </c>
+      <c r="AI4">
+        <v>0.2197783130562587</v>
+      </c>
+      <c r="AJ4">
+        <v>-0.1239735643443677</v>
+      </c>
+      <c r="AK4">
+        <v>-2.552514174179756</v>
+      </c>
+      <c r="AL4">
+        <v>0</v>
+      </c>
+      <c r="AM4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
           <t>Banco do Brasil S.A. (BOVESPA:BBAS3)</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>Bank (Money Center)</t>
         </is>
       </c>
-      <c r="D4">
+      <c r="D5">
         <v>0.118</v>
       </c>
-      <c r="E4">
+      <c r="E5">
         <v>0.142</v>
       </c>
-      <c r="F4">
+      <c r="F5">
         <v>0.0281</v>
       </c>
-      <c r="G4">
-        <v>0</v>
-      </c>
-      <c r="H4">
-        <v>0</v>
-      </c>
-      <c r="I4">
-        <v>0</v>
-      </c>
-      <c r="J4">
-        <v>0</v>
-      </c>
-      <c r="K4">
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5">
         <v>5797.9</v>
       </c>
-      <c r="L4">
+      <c r="L5">
         <v>0.284735591089459</v>
       </c>
-      <c r="M4">
+      <c r="M5">
         <v>1303.4</v>
       </c>
-      <c r="N4">
+      <c r="N5">
         <v>0.05843139891959743</v>
       </c>
-      <c r="O4">
+      <c r="O5">
         <v>0.2248055330378241</v>
       </c>
-      <c r="P4">
+      <c r="P5">
         <v>1303.4</v>
       </c>
-      <c r="Q4">
+      <c r="Q5">
         <v>0.05843139891959743</v>
       </c>
-      <c r="R4">
+      <c r="R5">
         <v>0.2248055330378241</v>
       </c>
-      <c r="S4">
-        <v>0</v>
-      </c>
-      <c r="T4">
-        <v>0</v>
-      </c>
-      <c r="U4">
+      <c r="S5">
+        <v>0</v>
+      </c>
+      <c r="T5">
+        <v>0</v>
+      </c>
+      <c r="U5">
         <v>13999.8</v>
       </c>
-      <c r="V4">
+      <c r="V5">
         <v>0.6276107860937394</v>
       </c>
-      <c r="W4">
+      <c r="W5">
         <v>0.1747587154801878</v>
       </c>
-      <c r="X4">
-        <v>0.2574691244584706</v>
-      </c>
-      <c r="Y4">
-        <v>-0.08271040897828275</v>
-      </c>
-      <c r="Z4">
+      <c r="X5">
+        <v>0.2574370501742179</v>
+      </c>
+      <c r="Y5">
+        <v>-0.08267833469403008</v>
+      </c>
+      <c r="Z5">
         <v>0.08907272919745132</v>
       </c>
-      <c r="AA4">
-        <v>0</v>
-      </c>
-      <c r="AB4">
-        <v>0.07834936727311964</v>
-      </c>
-      <c r="AC4">
-        <v>-0.07834936727311964</v>
-      </c>
-      <c r="AD4">
+      <c r="AA5">
+        <v>0</v>
+      </c>
+      <c r="AB5">
+        <v>0.07834619221656411</v>
+      </c>
+      <c r="AC5">
+        <v>-0.07834619221656411</v>
+      </c>
+      <c r="AD5">
         <v>203032.8</v>
       </c>
-      <c r="AE4">
-        <v>0</v>
-      </c>
-      <c r="AF4">
+      <c r="AE5">
+        <v>0</v>
+      </c>
+      <c r="AF5">
         <v>203032.8</v>
       </c>
-      <c r="AG4">
+      <c r="AG5">
         <v>189033</v>
       </c>
-      <c r="AH4">
+      <c r="AH5">
         <v>0.9010092780087627</v>
       </c>
-      <c r="AI4">
+      <c r="AI5">
         <v>0.8550481171134028</v>
       </c>
-      <c r="AJ4">
+      <c r="AJ5">
         <v>0.8944518180463188</v>
       </c>
-      <c r="AK4">
+      <c r="AK5">
         <v>0.8459665404800403</v>
       </c>
-      <c r="AL4">
-        <v>0</v>
-      </c>
-      <c r="AM4">
-        <v>0</v>
+      <c r="AL5">
+        <v>0</v>
+      </c>
+      <c r="AM5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Alfa Holdings S.A. (BOVESPA:RPAD3)</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="K6">
+        <v>-14.9</v>
+      </c>
+      <c r="M6">
+        <v>1.5</v>
+      </c>
+      <c r="N6">
+        <v>0.01710376282782212</v>
+      </c>
+      <c r="O6">
+        <v>-0.1006711409395973</v>
+      </c>
+      <c r="P6">
+        <v>1.5</v>
+      </c>
+      <c r="Q6">
+        <v>0.01710376282782212</v>
+      </c>
+      <c r="R6">
+        <v>-0.1006711409395973</v>
+      </c>
+      <c r="S6">
+        <v>0</v>
+      </c>
+      <c r="T6">
+        <v>0</v>
+      </c>
+      <c r="U6">
+        <v>0.02</v>
+      </c>
+      <c r="V6">
+        <v>0.0002280501710376283</v>
+      </c>
+      <c r="W6">
+        <v>-0.06760435571687841</v>
+      </c>
+      <c r="X6">
+        <v>0.07600240416200947</v>
+      </c>
+      <c r="Y6">
+        <v>-0.1436067598788879</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+      <c r="AA6">
+        <v>-0.007533845574319571</v>
+      </c>
+      <c r="AB6">
+        <v>0.07600240416200947</v>
+      </c>
+      <c r="AC6">
+        <v>-0.08353624973632905</v>
+      </c>
+      <c r="AD6">
+        <v>0</v>
+      </c>
+      <c r="AE6">
+        <v>0</v>
+      </c>
+      <c r="AF6">
+        <v>0</v>
+      </c>
+      <c r="AG6">
+        <v>-0.02</v>
+      </c>
+      <c r="AH6">
+        <v>0</v>
+      </c>
+      <c r="AI6">
+        <v>0</v>
+      </c>
+      <c r="AJ6">
+        <v>-0.0002281021897810219</v>
+      </c>
+      <c r="AK6">
+        <v>-0.0001080030240846744</v>
+      </c>
+      <c r="AL6">
+        <v>0</v>
+      </c>
+      <c r="AM6">
+        <v>-1.26</v>
+      </c>
+      <c r="AQ6">
+        <v>1.317460317460317</v>
       </c>
     </row>
   </sheetData>
